--- a/80_인수인계_프로젝트완료 및 유지보수용/08_현업공유_산출물/30_output_share/06_BRONZE노출감사.xlsx
+++ b/80_인수인계_프로젝트완료 및 유지보수용/08_현업공유_산출물/30_output_share/06_BRONZE노출감사.xlsx
@@ -544,7 +544,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BRONZE 노출감사 — 전 원천 1314컬럼 (2026-10-25)</t>
+          <t>BRONZE 노출감사 — 전 원천 1314컬럼 (2026-10-27)</t>
         </is>
       </c>
     </row>
